--- a/outputs/evaluation/decision/v2/CF_M05/run_1/CF_M05_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M05/run_1/CF_M05_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5</v>
+        <v>0.8889</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2308</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8976</v>
+        <v>0.9206</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1333</v>
+        <v>0.3125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6667</v>
+        <v>0.6875</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.9234</v>
       </c>
     </row>
     <row r="8">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6667</v>
+        <v>0.625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5</v>
+        <v>0.8889</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2308</v>
+        <v>0.6153999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -726,19 +726,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -755,31 +755,31 @@
         <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -792,31 +792,31 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
         <v>6</v>
       </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,22 +974,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M05_AD01</t>
+          <t>CF_M05_AD06</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.857</v>
+        <v>0.8214</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -1012,24 +1012,26 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
+          <t>It offers flexibility, scalability, and cost reduction, as it eliminates the need for local infrastructure.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Technology cloud</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1039,48 +1041,48 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
+          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M05_P01</t>
+          <t>CF_M05_P05</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M05_AD06</t>
+          <t>CF_M05_AD01</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9115</v>
+        <v>0.86</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1088,144 +1090,569 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>The use of this architecture allows high scalability, availability, and accessibility, as resource management can be done according to needs and anywhere with an Internet connection.</t>
+          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and system evolution.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Technology cloud, Scalability, Availability</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>AU_17, AU_18, AU_19</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
+          <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CF_M05_P05</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>AD_08</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CF_M05_AD12</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8673</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated. This structure clarifies roles, avoids unnecessary coupling, and facilitates testing, reusing, and maintaining the code over time.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CF_M05_AD03</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9026999999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.8804</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>This ensures that the presentation layer is available and updated, facilitating deployment and reducing dependence on external elements. In this way, the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>C_01</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>CF_M05_C01, *CF_M05_C12</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CF_M05_AU02</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CF_M05_AD08</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9245</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD_09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CF_M05_AD11</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9933999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>It allows automating the deployment, scaling, and management of applications running in containers, running thousands of containers on different servers, and ensuring high availability.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>C_06, C_07</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>AU_18, AU_19</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>CF_M05_AU07</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CF_M05_AD04</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9954</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.8605</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>This microservice is essential to maintain the confidentiality and protection of data.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>R_48</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>*CF_M05_C11</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU03</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>AD_03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CF_M05_AD08</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.9245</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CF_M05_AD02</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>CF_M05_P02</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>61</v>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.7994</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>R_48</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>CF_M05_C09 , *CF_M05_C11</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU01</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1239,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,12 +1709,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
+          <t>Angular applies the MVVM pattern, as its architecture is based on components and services.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1311,77 +1738,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6768999999999999</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AD_05</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Maintainability</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CF_M05_AD12</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.7287</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AWS manages multiple levels of security and offers tools to protect data and infrastructures, facilitating compliance with legal regulations and international standards.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CF_M05_AD02</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6804</v>
       </c>
     </row>
   </sheetData>
@@ -1395,7 +1752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1438,331 +1795,166 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_AD02</t>
+          <t>CF_M05_AD05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
+          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CF_M05_C09 , *CF_M05_C11</t>
+          <t>*CF_M05_C13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M05_AU01</t>
+          <t>CF_M05_AU04</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.7321</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AD03</t>
+          <t>CF_M05_AD07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CF_M05_C01, *CF_M05_C12</t>
+          <t>*CF_M05_C15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M05_AU02</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6857</v>
+        <v>0.8676</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
+          <t>CF_M05_AD09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M05_C11</t>
+          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_09</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.6784</v>
+        <v>0.7203000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_AD10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>*CF_M05_C13</t>
+          <t>*CF_M05_C14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_AU30, CF_M05_AU29</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_08</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.6686</v>
+        <v>0.7083</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AD07</t>
+          <t>CF_M05_AD13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+          <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>*CF_M05_C15</t>
+          <t>*CF_M05_C18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU07</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8676</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CF_M05_AD09</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU30</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>76</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0.7176</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CF_M05_AD10</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>*CF_M05_C14</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CF_M05_AU30, CF_M05_AU29</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>77</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>AD_04</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0.6768999999999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CF_M05_AD11</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CF_M05_C06, CF_M05_C07</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CF_M05_AU07</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>81</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0.7877999999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M05_AD12</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>*CF_M05_C14</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU29</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>78</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0.7494</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M05_AD13</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>*CF_M05_C18</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CF_M05_AU07</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>82</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
     </row>
   </sheetData>
